--- a/artfynd/A 29234-2026 artfynd.xlsx
+++ b/artfynd/A 29234-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182724</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182726</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182718</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182730</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182715</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182720</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,6 +1474,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182722</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1546,8 +1586,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182728</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29234-2026 artfynd.xlsx
+++ b/artfynd/A 29234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182724</v>
       </c>
       <c r="B2" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135182726</v>
       </c>
       <c r="B3" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135182718</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>135182730</v>
       </c>
       <c r="B5" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>135182715</v>
       </c>
       <c r="B6" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>135182720</v>
       </c>
       <c r="B7" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>135182722</v>
       </c>
       <c r="B8" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>135182728</v>
       </c>
       <c r="B9" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29234-2026 artfynd.xlsx
+++ b/artfynd/A 29234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182724</v>
       </c>
       <c r="B2" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135182726</v>
       </c>
       <c r="B3" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>135182730</v>
       </c>
       <c r="B5" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>135182715</v>
       </c>
       <c r="B6" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>135182720</v>
       </c>
       <c r="B7" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>135182722</v>
       </c>
       <c r="B8" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>135182728</v>
       </c>
       <c r="B9" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29234-2026 artfynd.xlsx
+++ b/artfynd/A 29234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182724</v>
       </c>
       <c r="B2" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135182726</v>
       </c>
       <c r="B3" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>135182730</v>
       </c>
       <c r="B5" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>135182715</v>
       </c>
       <c r="B6" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>135182720</v>
       </c>
       <c r="B7" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135182722</v>
       </c>
       <c r="B8" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>135182728</v>
       </c>
       <c r="B9" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29234-2026 artfynd.xlsx
+++ b/artfynd/A 29234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182724</v>
       </c>
       <c r="B2" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135182726</v>
       </c>
       <c r="B3" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135182718</v>
       </c>
       <c r="B4" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>135182730</v>
       </c>
       <c r="B5" t="n">
-        <v>99180</v>
+        <v>99197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>135182715</v>
       </c>
       <c r="B6" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>135182720</v>
       </c>
       <c r="B7" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135182722</v>
       </c>
       <c r="B8" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>135182728</v>
       </c>
       <c r="B9" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29234-2026 artfynd.xlsx
+++ b/artfynd/A 29234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182724</v>
       </c>
       <c r="B2" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135182726</v>
       </c>
       <c r="B3" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>135182730</v>
       </c>
       <c r="B5" t="n">
-        <v>99197</v>
+        <v>99198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>135182715</v>
       </c>
       <c r="B6" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>135182720</v>
       </c>
       <c r="B7" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135182722</v>
       </c>
       <c r="B8" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>135182728</v>
       </c>
       <c r="B9" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29234-2026 artfynd.xlsx
+++ b/artfynd/A 29234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182724</v>
       </c>
       <c r="B2" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135182726</v>
       </c>
       <c r="B3" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>135182730</v>
       </c>
       <c r="B5" t="n">
-        <v>99198</v>
+        <v>99199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>135182715</v>
       </c>
       <c r="B6" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>135182720</v>
       </c>
       <c r="B7" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135182722</v>
       </c>
       <c r="B8" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>135182728</v>
       </c>
       <c r="B9" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29234-2026 artfynd.xlsx
+++ b/artfynd/A 29234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182724</v>
       </c>
       <c r="B2" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135182726</v>
       </c>
       <c r="B3" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135182718</v>
       </c>
       <c r="B4" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>135182730</v>
       </c>
       <c r="B5" t="n">
-        <v>99199</v>
+        <v>99200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>135182715</v>
       </c>
       <c r="B6" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>135182720</v>
       </c>
       <c r="B7" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135182722</v>
       </c>
       <c r="B8" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>135182728</v>
       </c>
       <c r="B9" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29234-2026 artfynd.xlsx
+++ b/artfynd/A 29234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182724</v>
       </c>
       <c r="B2" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135182726</v>
       </c>
       <c r="B3" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135182718</v>
       </c>
       <c r="B4" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>135182730</v>
       </c>
       <c r="B5" t="n">
-        <v>99200</v>
+        <v>99206</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>135182715</v>
       </c>
       <c r="B6" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>135182720</v>
       </c>
       <c r="B7" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135182722</v>
       </c>
       <c r="B8" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>135182728</v>
       </c>
       <c r="B9" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29234-2026 artfynd.xlsx
+++ b/artfynd/A 29234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182724</v>
       </c>
       <c r="B2" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135182726</v>
       </c>
       <c r="B3" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135182718</v>
       </c>
       <c r="B4" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>135182730</v>
       </c>
       <c r="B5" t="n">
-        <v>99206</v>
+        <v>99207</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>135182715</v>
       </c>
       <c r="B6" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>135182720</v>
       </c>
       <c r="B7" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135182722</v>
       </c>
       <c r="B8" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>135182728</v>
       </c>
       <c r="B9" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29234-2026 artfynd.xlsx
+++ b/artfynd/A 29234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182724</v>
       </c>
       <c r="B2" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135182726</v>
       </c>
       <c r="B3" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>135182730</v>
       </c>
       <c r="B5" t="n">
-        <v>99207</v>
+        <v>99218</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>135182715</v>
       </c>
       <c r="B6" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>135182720</v>
       </c>
       <c r="B7" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135182722</v>
       </c>
       <c r="B8" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>135182728</v>
       </c>
       <c r="B9" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29234-2026 artfynd.xlsx
+++ b/artfynd/A 29234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182724</v>
       </c>
       <c r="B2" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135182726</v>
       </c>
       <c r="B3" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135182718</v>
       </c>
       <c r="B4" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>135182730</v>
       </c>
       <c r="B5" t="n">
-        <v>99218</v>
+        <v>99231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>135182715</v>
       </c>
       <c r="B6" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>135182720</v>
       </c>
       <c r="B7" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135182722</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>135182728</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29234-2026 artfynd.xlsx
+++ b/artfynd/A 29234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182724</v>
       </c>
       <c r="B2" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135182726</v>
       </c>
       <c r="B3" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>135182730</v>
       </c>
       <c r="B5" t="n">
-        <v>99231</v>
+        <v>99232</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>135182715</v>
       </c>
       <c r="B6" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>135182720</v>
       </c>
       <c r="B7" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135182722</v>
       </c>
       <c r="B8" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>135182728</v>
       </c>
       <c r="B9" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
